--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-006_申請一覧取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-006_申請一覧取得_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="7191375"/>
+    <ext cx="8572500" cy="7400925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-006 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-006 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="49" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1766,7 +1766,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：RequestService#toIso を AppTime#toIso（ONL-002 定義）に変更し toSummary から参照、updated_at をトリガ自動更新に変更、認証なしを 401 / E-001 の JSON に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：RequestService#toIso を AppTime#toIso（ONL-002 定義）に変更し toSummary から参照、updated_at をトリガ自動更新に変更、認証なしを 401 / E-001 の JSON に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3597,7 +3598,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public RequestListResponse list(@AuthenticationPrincipal Jwt jwt, @RequestParam(required = false) String status)</t>
+          <t>public RequestListResponse list(Authentication auth, @RequestParam(required = false) String status)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -3660,17 +3661,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン（sub = users.id）</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -3737,7 +3738,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return requestService.list(userId, status);</t>
         </is>
       </c>
